--- a/artfynd/S 1413-2026 artfynd.xlsx
+++ b/artfynd/S 1413-2026 artfynd.xlsx
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97884935</v>
+        <v>97884791</v>
       </c>
       <c r="B28" t="n">
-        <v>88345</v>
+        <v>89206</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4566</v>
+        <v>4393</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dofttråding</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Inosperma bongardii</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495449</v>
+        <v>495469</v>
       </c>
       <c r="R28" t="n">
-        <v>6567547</v>
+        <v>6567485</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3422,6 +3422,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3439,16 +3440,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884935</t>
+          <t>https://artportalen.se/Sighting/97884791</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97884747</v>
+        <v>97884935</v>
       </c>
       <c r="B29" t="n">
-        <v>92869</v>
+        <v>88345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3456,21 +3457,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>4566</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttråding</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Inosperma bongardii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3480,10 +3481,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495381</v>
+        <v>495449</v>
       </c>
       <c r="R29" t="n">
-        <v>6567558</v>
+        <v>6567547</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3541,16 +3542,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884747</t>
+          <t>https://artportalen.se/Sighting/97884935</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97884878</v>
+        <v>97884747</v>
       </c>
       <c r="B30" t="n">
-        <v>91087</v>
+        <v>92869</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,21 +3559,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4823</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hasselsopp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leccinellum pseudoscabrum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kallenb.) Mikšík</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3582,10 +3583,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495449</v>
+        <v>495381</v>
       </c>
       <c r="R30" t="n">
-        <v>6567515</v>
+        <v>6567558</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3643,13 +3644,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884878</t>
+          <t>https://artportalen.se/Sighting/97884747</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>97884879</v>
+        <v>97884878</v>
       </c>
       <c r="B31" t="n">
         <v>91087</v>
@@ -3684,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495495</v>
+        <v>495449</v>
       </c>
       <c r="R31" t="n">
-        <v>6567556</v>
+        <v>6567515</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3745,13 +3746,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884879</t>
+          <t>https://artportalen.se/Sighting/97884878</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>97884880</v>
+        <v>97884879</v>
       </c>
       <c r="B32" t="n">
         <v>91087</v>
@@ -3786,10 +3787,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495494</v>
+        <v>495495</v>
       </c>
       <c r="R32" t="n">
-        <v>6567565</v>
+        <v>6567556</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3847,13 +3848,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884880</t>
+          <t>https://artportalen.se/Sighting/97884879</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>97884881</v>
+        <v>97884880</v>
       </c>
       <c r="B33" t="n">
         <v>91087</v>
@@ -3888,10 +3889,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495614</v>
+        <v>495494</v>
       </c>
       <c r="R33" t="n">
-        <v>6567592</v>
+        <v>6567565</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3949,13 +3950,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884881</t>
+          <t>https://artportalen.se/Sighting/97884880</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>97884882</v>
+        <v>97884881</v>
       </c>
       <c r="B34" t="n">
         <v>91087</v>
@@ -3990,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495624</v>
+        <v>495614</v>
       </c>
       <c r="R34" t="n">
-        <v>6567583</v>
+        <v>6567592</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4051,16 +4052,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884882</t>
+          <t>https://artportalen.se/Sighting/97884881</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>97884760</v>
+        <v>97884882</v>
       </c>
       <c r="B35" t="n">
-        <v>89887</v>
+        <v>91087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4068,21 +4069,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5567</v>
+        <v>4823</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sprickskölding</t>
+          <t>Hasselsopp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pluteus ephebeus</t>
+          <t>Leccinellum pseudoscabrum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Gillet</t>
+          <t>(Kallenb.) Mikšík</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4092,10 +4093,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495383</v>
+        <v>495624</v>
       </c>
       <c r="R35" t="n">
-        <v>6567542</v>
+        <v>6567583</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4153,16 +4154,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884760</t>
+          <t>https://artportalen.se/Sighting/97884882</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>97884764</v>
+        <v>97884760</v>
       </c>
       <c r="B36" t="n">
-        <v>89007</v>
+        <v>89887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4170,19 +4171,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5757</v>
+        <v>5567</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Snövit fingersvamp</t>
+          <t>Sprickskölding</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramariopsis kunzei s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Pluteus ephebeus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Gillet</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4190,10 +4195,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495476</v>
+        <v>495383</v>
       </c>
       <c r="R36" t="n">
-        <v>6567555</v>
+        <v>6567542</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4251,16 +4256,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884764</t>
+          <t>https://artportalen.se/Sighting/97884760</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>97884892</v>
+        <v>97884764</v>
       </c>
       <c r="B37" t="n">
-        <v>92928</v>
+        <v>89007</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4268,23 +4273,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5836</v>
+        <v>5757</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Snövit fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Pers.</t>
-        </is>
-      </c>
+          <t>Ramariopsis kunzei s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4292,10 +4293,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495415</v>
+        <v>495476</v>
       </c>
       <c r="R37" t="n">
-        <v>6567496</v>
+        <v>6567555</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4353,13 +4354,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884892</t>
+          <t>https://artportalen.se/Sighting/97884764</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>97884893</v>
+        <v>97884892</v>
       </c>
       <c r="B38" t="n">
         <v>92928</v>
@@ -4394,10 +4395,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495531</v>
+        <v>495415</v>
       </c>
       <c r="R38" t="n">
-        <v>6567577</v>
+        <v>6567496</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4455,13 +4456,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884893</t>
+          <t>https://artportalen.se/Sighting/97884892</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>97884894</v>
+        <v>97884893</v>
       </c>
       <c r="B39" t="n">
         <v>92928</v>
@@ -4496,10 +4497,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495558</v>
+        <v>495531</v>
       </c>
       <c r="R39" t="n">
-        <v>6567592</v>
+        <v>6567577</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4557,38 +4558,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884894</t>
+          <t>https://artportalen.se/Sighting/97884893</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>97884885</v>
+        <v>97884894</v>
       </c>
       <c r="B40" t="n">
-        <v>83314</v>
+        <v>92928</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6471</v>
+        <v>5836</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4598,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495472</v>
+        <v>495558</v>
       </c>
       <c r="R40" t="n">
-        <v>6567433</v>
+        <v>6567592</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4659,13 +4660,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884885</t>
+          <t>https://artportalen.se/Sighting/97884894</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>97884886</v>
+        <v>97884885</v>
       </c>
       <c r="B41" t="n">
         <v>83314</v>
@@ -4700,10 +4701,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495423</v>
+        <v>495472</v>
       </c>
       <c r="R41" t="n">
-        <v>6567544</v>
+        <v>6567433</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4761,13 +4762,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884886</t>
+          <t>https://artportalen.se/Sighting/97884885</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>97884887</v>
+        <v>97884886</v>
       </c>
       <c r="B42" t="n">
         <v>83314</v>
@@ -4802,10 +4803,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495414</v>
+        <v>495423</v>
       </c>
       <c r="R42" t="n">
-        <v>6567562</v>
+        <v>6567544</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4863,16 +4864,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884887</t>
+          <t>https://artportalen.se/Sighting/97884886</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134205907</v>
+        <v>97884887</v>
       </c>
       <c r="B43" t="n">
-        <v>43288</v>
+        <v>83314</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4880,63 +4881,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100770</v>
+        <v>6471</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre blåvinge</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cupido minimus</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fuessly, 1775)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lanna badgruva, Nrk</t>
+          <t>Vintrosa lövskogar, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495524</v>
+        <v>495414</v>
       </c>
       <c r="R43" t="n">
-        <v>6567430</v>
+        <v>6567562</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4963,12 +4935,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2018-08-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4977,69 +4949,97 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134205907</t>
+          <t>https://artportalen.se/Sighting/97884887</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>97884774</v>
+        <v>134205907</v>
       </c>
       <c r="B44" t="n">
-        <v>99096</v>
+        <v>43288</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>100770</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre blåvinge</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cupido minimus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fuessly, 1775)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vintrosa lövskogar, Nrk</t>
+          <t>Lanna badgruva, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495413</v>
+        <v>495524</v>
       </c>
       <c r="R44" t="n">
-        <v>6567548</v>
+        <v>6567430</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5066,12 +5066,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,33 +5080,34 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884774</t>
+          <t>https://artportalen.se/Sighting/134205907</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>97884795</v>
+        <v>97884774</v>
       </c>
       <c r="B45" t="n">
-        <v>99141</v>
+        <v>99096</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5114,21 +5115,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5138,10 +5139,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495507</v>
+        <v>495413</v>
       </c>
       <c r="R45" t="n">
-        <v>6567540</v>
+        <v>6567548</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5199,13 +5200,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884795</t>
+          <t>https://artportalen.se/Sighting/97884774</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>97884796</v>
+        <v>97884795</v>
       </c>
       <c r="B46" t="n">
         <v>99141</v>
@@ -5240,10 +5241,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495494</v>
+        <v>495507</v>
       </c>
       <c r="R46" t="n">
-        <v>6567576</v>
+        <v>6567540</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5301,13 +5302,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884796</t>
+          <t>https://artportalen.se/Sighting/97884795</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>97884797</v>
+        <v>97884796</v>
       </c>
       <c r="B47" t="n">
         <v>99141</v>
@@ -5342,10 +5343,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495631</v>
+        <v>495494</v>
       </c>
       <c r="R47" t="n">
-        <v>6567585</v>
+        <v>6567576</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5403,69 +5404,54 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884797</t>
+          <t>https://artportalen.se/Sighting/97884796</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>61006340</v>
+        <v>97884797</v>
       </c>
       <c r="B48" t="n">
-        <v>108194</v>
+        <v>99141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220103</v>
+        <v>219862</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lanna badgruva, Nrk</t>
+          <t>Vintrosa lövskogar, Nrk</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495507</v>
+        <v>495631</v>
       </c>
       <c r="R48" t="n">
-        <v>6567420</v>
+        <v>6567585</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5487,24 +5473,14 @@
           <t>Hidinge</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Lek-0043</t>
-        </is>
-      </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2018-08-12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor varav 25 hade blomstänglar.</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5515,40 +5491,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Skogsbryn. Kalkhaltig mark.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Gunnel Gustafson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Gunnel Gustafson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61006340</t>
+          <t>https://artportalen.se/Sighting/97884797</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>97884763</v>
+        <v>61006340</v>
       </c>
       <c r="B49" t="n">
-        <v>109866</v>
+        <v>108194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5556,37 +5523,52 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220228</v>
+        <v>220103</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vintrosa lövskogar, Nrk</t>
+          <t>Lanna badgruva, Nrk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495604</v>
+        <v>495507</v>
       </c>
       <c r="R49" t="n">
-        <v>6567576</v>
+        <v>6567420</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5608,14 +5590,24 @@
           <t>Hidinge</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Lek-0043</t>
+        </is>
+      </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>2016-06-05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2016-06-05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor varav 25 hade blomstänglar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5626,31 +5618,40 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Skogsbryn. Kalkhaltig mark.</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Gunnel Gustafson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Gunnel Gustafson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884763</t>
+          <t>https://artportalen.se/Sighting/61006340</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>101073332</v>
+        <v>97884763</v>
       </c>
       <c r="B50" t="n">
-        <v>110078</v>
+        <v>109866</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5658,16 +5659,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5675,36 +5676,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lanna badgruva, N sluttningen, Nrk</t>
+          <t>Vintrosa lövskogar, Nrk</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495596</v>
+        <v>495604</v>
       </c>
       <c r="R50" t="n">
-        <v>6567579</v>
+        <v>6567576</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5726,24 +5711,14 @@
           <t>Hidinge</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Lek-0073</t>
-        </is>
-      </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2018-08-12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ca 25 blommande stjälkar samt ett flertal bladrosetter utan stjälkar. I och upp på norra skärningen/kanten strax ost om lilla stigen.</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5752,72 +5727,87 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Öppen solexponerad sydskärning.</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101073332</t>
+          <t>https://artportalen.se/Sighting/97884763</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>97884791</v>
+        <v>101073332</v>
       </c>
       <c r="B51" t="n">
-        <v>89060</v>
+        <v>110078</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>239221</v>
+        <v>220299</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vintrosa lövskogar, Nrk</t>
+          <t>Lanna badgruva, N sluttningen, Nrk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495469</v>
+        <v>495596</v>
       </c>
       <c r="R51" t="n">
-        <v>6567485</v>
+        <v>6567579</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5839,14 +5829,24 @@
           <t>Hidinge</t>
         </is>
       </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Lek-0073</t>
+        </is>
+      </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ca 25 blommande stjälkar samt ett flertal bladrosetter utan stjälkar. I och upp på norra skärningen/kanten strax ost om lilla stigen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5859,21 +5859,30 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Öppen solexponerad sydskärning.</t>
+        </is>
+      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97884791</t>
+          <t>https://artportalen.se/Sighting/101073332</t>
         </is>
       </c>
     </row>

--- a/artfynd/S 1413-2026 artfynd.xlsx
+++ b/artfynd/S 1413-2026 artfynd.xlsx
@@ -3346,7 +3346,7 @@
         <v>97884791</v>
       </c>
       <c r="B28" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
